--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/139.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/139.xlsx
@@ -426,13 +426,13 @@
         <v>5.747827661701244</v>
       </c>
       <c r="E2">
-        <v>-15.78263349665514</v>
+        <v>-20.5409510986659</v>
       </c>
       <c r="F2">
-        <v>-0.5162080630782561</v>
+        <v>-3.69133700453915</v>
       </c>
       <c r="G2">
-        <v>-17.81623616764472</v>
+        <v>-15.42279690257275</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>5.583556852448289</v>
       </c>
       <c r="E3">
-        <v>-17.77078406427321</v>
+        <v>-22.17649817801735</v>
       </c>
       <c r="F3">
-        <v>-1.613104841741069</v>
+        <v>-3.543683000092346</v>
       </c>
       <c r="G3">
-        <v>-16.29526336226476</v>
+        <v>-15.20506994127997</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>5.364132526145439</v>
       </c>
       <c r="E4">
-        <v>-18.28608960618999</v>
+        <v>-23.04287882643321</v>
       </c>
       <c r="F4">
-        <v>-2.527653932393029</v>
+        <v>-3.705248606701765</v>
       </c>
       <c r="G4">
-        <v>-16.79118735106969</v>
+        <v>-15.68785927404701</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>5.116037439114372</v>
       </c>
       <c r="E5">
-        <v>-20.13296038417137</v>
+        <v>-21.26718163092542</v>
       </c>
       <c r="F5">
-        <v>-1.306026560421084</v>
+        <v>-3.428209412509498</v>
       </c>
       <c r="G5">
-        <v>-15.91547704122322</v>
+        <v>-15.70902196970257</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>4.845222130643826</v>
       </c>
       <c r="E6">
-        <v>-22.06003797925784</v>
+        <v>-24.02428681570152</v>
       </c>
       <c r="F6">
-        <v>-0.294811135699435</v>
+        <v>-3.646298668848941</v>
       </c>
       <c r="G6">
-        <v>-15.93992927506359</v>
+        <v>-16.25502656662653</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>4.569459957077196</v>
       </c>
       <c r="E7">
-        <v>-20.93558093232846</v>
+        <v>-24.83593644527879</v>
       </c>
       <c r="F7">
-        <v>-1.517744014698193</v>
+        <v>-3.474930162394793</v>
       </c>
       <c r="G7">
-        <v>-15.459359075199</v>
+        <v>-16.80882162541036</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>4.302263698054746</v>
       </c>
       <c r="E8">
-        <v>-21.93422059538348</v>
+        <v>-25.73216622348619</v>
       </c>
       <c r="F8">
-        <v>-0.8579510351031922</v>
+        <v>-2.909079016481673</v>
       </c>
       <c r="G8">
-        <v>-16.73549233670747</v>
+        <v>-16.26899405018898</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>4.056113794178343</v>
       </c>
       <c r="E9">
-        <v>-23.57081843720012</v>
+        <v>-26.75427983694914</v>
       </c>
       <c r="F9">
-        <v>-1.298053524169139</v>
+        <v>-2.979954131465199</v>
       </c>
       <c r="G9">
-        <v>-16.4856519115717</v>
+        <v>-15.93184771518179</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>3.841833280994927</v>
       </c>
       <c r="E10">
-        <v>-24.1707664259169</v>
+        <v>-26.71076248868759</v>
       </c>
       <c r="F10">
-        <v>-0.9864473866254514</v>
+        <v>-2.825843831480976</v>
       </c>
       <c r="G10">
-        <v>-15.59139748289455</v>
+        <v>-16.54010551688085</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>3.670816510069727</v>
       </c>
       <c r="E11">
-        <v>-25.8700362266252</v>
+        <v>-28.41830340974928</v>
       </c>
       <c r="F11">
-        <v>-0.02506820159102639</v>
+        <v>-2.233902425849283</v>
       </c>
       <c r="G11">
-        <v>-14.1775056722914</v>
+        <v>-15.72831145611401</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>3.550845729528515</v>
       </c>
       <c r="E12">
-        <v>-24.20445727618391</v>
+        <v>-27.81678758375738</v>
       </c>
       <c r="F12">
-        <v>0.09523973815455981</v>
+        <v>-2.404522916538703</v>
       </c>
       <c r="G12">
-        <v>-14.23146845761742</v>
+        <v>-16.11535434174656</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>3.484377496229344</v>
       </c>
       <c r="E13">
-        <v>-27.47432623754599</v>
+        <v>-29.13403462377963</v>
       </c>
       <c r="F13">
-        <v>0.6502699206849097</v>
+        <v>-1.963389110056271</v>
       </c>
       <c r="G13">
-        <v>-15.04437861169695</v>
+        <v>-15.61409921248658</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.474875457690185</v>
       </c>
       <c r="E14">
-        <v>-22.80578860474405</v>
+        <v>-29.55058510681464</v>
       </c>
       <c r="F14">
-        <v>0.3553421324291878</v>
+        <v>-1.831420242381476</v>
       </c>
       <c r="G14">
-        <v>-12.99831980042933</v>
+        <v>-15.78440199828179</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.523101978226981</v>
       </c>
       <c r="E15">
-        <v>-25.91256095738012</v>
+        <v>-32.17811840467874</v>
       </c>
       <c r="F15">
-        <v>0.5574298156487524</v>
+        <v>-1.196714369580258</v>
       </c>
       <c r="G15">
-        <v>-13.10176402799072</v>
+        <v>-15.20199056803476</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.622870733566058</v>
       </c>
       <c r="E16">
-        <v>-30.3796221556033</v>
+        <v>-31.74234062981544</v>
       </c>
       <c r="F16">
-        <v>0.7681043553657366</v>
+        <v>-1.198240222336215</v>
       </c>
       <c r="G16">
-        <v>-12.27138929796893</v>
+        <v>-14.24648154438861</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.764716100212375</v>
       </c>
       <c r="E17">
-        <v>-28.96897977591396</v>
+        <v>-33.68510075086446</v>
       </c>
       <c r="F17">
-        <v>0.9953371310972802</v>
+        <v>-1.135879067518663</v>
       </c>
       <c r="G17">
-        <v>-10.48363102968458</v>
+        <v>-13.62081790850061</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.93696038349525</v>
       </c>
       <c r="E18">
-        <v>-29.90650285771847</v>
+        <v>-34.93768852037613</v>
       </c>
       <c r="F18">
-        <v>0.3031732101356805</v>
+        <v>-0.7299111140198753</v>
       </c>
       <c r="G18">
-        <v>-11.57031691531121</v>
+        <v>-12.76448715575397</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.124630938571304</v>
       </c>
       <c r="E19">
-        <v>-31.37663583642465</v>
+        <v>-35.95213530573345</v>
       </c>
       <c r="F19">
-        <v>1.102864190185073</v>
+        <v>-0.7912972804043327</v>
       </c>
       <c r="G19">
-        <v>-11.38390061389965</v>
+        <v>-12.9094892157167</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.308698666485783</v>
       </c>
       <c r="E20">
-        <v>-35.23013274260261</v>
+        <v>-36.35916662841195</v>
       </c>
       <c r="F20">
-        <v>1.485949322548927</v>
+        <v>-0.1061604001206812</v>
       </c>
       <c r="G20">
-        <v>-10.45881329160146</v>
+        <v>-11.38950979865366</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.472091179114725</v>
       </c>
       <c r="E21">
-        <v>-33.08600624707493</v>
+        <v>-37.49431819450276</v>
       </c>
       <c r="F21">
-        <v>1.571042535634103</v>
+        <v>0.08736859109315891</v>
       </c>
       <c r="G21">
-        <v>-10.73227181768073</v>
+        <v>-11.92543561608362</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.600492778393807</v>
       </c>
       <c r="E22">
-        <v>-36.44000888684973</v>
+        <v>-38.90271368686536</v>
       </c>
       <c r="F22">
-        <v>2.052996630991689</v>
+        <v>0.2769031946906998</v>
       </c>
       <c r="G22">
-        <v>-9.646211205383674</v>
+        <v>-11.23193569811243</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.67992844499616</v>
       </c>
       <c r="E23">
-        <v>-36.34306878131691</v>
+        <v>-38.59191019397748</v>
       </c>
       <c r="F23">
-        <v>2.97852655993516</v>
+        <v>0.5975774701928332</v>
       </c>
       <c r="G23">
-        <v>-9.216822042483273</v>
+        <v>-10.60786070030812</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.702311013037637</v>
       </c>
       <c r="E24">
-        <v>-37.83855711516117</v>
+        <v>-39.85665856624824</v>
       </c>
       <c r="F24">
-        <v>2.324981127292073</v>
+        <v>0.9669390397945076</v>
       </c>
       <c r="G24">
-        <v>-8.151561232343614</v>
+        <v>-9.612186676499991</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.666324123891081</v>
       </c>
       <c r="E25">
-        <v>-37.26473074907189</v>
+        <v>-41.07116969433388</v>
       </c>
       <c r="F25">
-        <v>2.675741706863885</v>
+        <v>0.216163154880426</v>
       </c>
       <c r="G25">
-        <v>-9.527601162492511</v>
+        <v>-9.568035069347378</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.575039123321056</v>
       </c>
       <c r="E26">
-        <v>-36.42287273692349</v>
+        <v>-40.18304490802688</v>
       </c>
       <c r="F26">
-        <v>2.720475203349864</v>
+        <v>1.090437022408275</v>
       </c>
       <c r="G26">
-        <v>-7.818982394998579</v>
+        <v>-10.15502052411804</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.433730108252733</v>
       </c>
       <c r="E27">
-        <v>-37.8342128561154</v>
+        <v>-40.2728913286169</v>
       </c>
       <c r="F27">
-        <v>2.649832031239121</v>
+        <v>0.7373023418600398</v>
       </c>
       <c r="G27">
-        <v>-9.569700724396508</v>
+        <v>-9.400495756701865</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.252559760302147</v>
       </c>
       <c r="E28">
-        <v>-38.95156168186234</v>
+        <v>-42.19681663630782</v>
       </c>
       <c r="F28">
-        <v>1.724098323914562</v>
+        <v>0.3973403597511227</v>
       </c>
       <c r="G28">
-        <v>-9.115016057152809</v>
+        <v>-9.508618438570526</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.041076115526644</v>
       </c>
       <c r="E29">
-        <v>-36.27313700902945</v>
+        <v>-41.08289420990387</v>
       </c>
       <c r="F29">
-        <v>2.29264166388678</v>
+        <v>0.6352201417108483</v>
       </c>
       <c r="G29">
-        <v>-8.285381473222603</v>
+        <v>-9.36824914488473</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.805631219823729</v>
       </c>
       <c r="E30">
-        <v>-38.6297833280486</v>
+        <v>-41.50912167532572</v>
       </c>
       <c r="F30">
-        <v>2.508626867023112</v>
+        <v>0.1342632981330417</v>
       </c>
       <c r="G30">
-        <v>-8.58349064973117</v>
+        <v>-8.986354647585861</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.553117075225258</v>
       </c>
       <c r="E31">
-        <v>-39.71212265893288</v>
+        <v>-40.20733704106581</v>
       </c>
       <c r="F31">
-        <v>1.195182423757467</v>
+        <v>0.1080752910609381</v>
       </c>
       <c r="G31">
-        <v>-7.785617079124151</v>
+        <v>-8.520823641938382</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.289737419533814</v>
       </c>
       <c r="E32">
-        <v>-37.6762641528265</v>
+        <v>-41.18652306227533</v>
       </c>
       <c r="F32">
-        <v>1.953123686705764</v>
+        <v>-0.1415523974052901</v>
       </c>
       <c r="G32">
-        <v>-7.788765637101034</v>
+        <v>-9.138833880057536</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.019504077589269</v>
       </c>
       <c r="E33">
-        <v>-35.77579410609255</v>
+        <v>-41.01811449626486</v>
       </c>
       <c r="F33">
-        <v>2.256715369627366</v>
+        <v>-0.04386302959314437</v>
       </c>
       <c r="G33">
-        <v>-6.822273210960078</v>
+        <v>-8.641219434129866</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.745432577407862</v>
       </c>
       <c r="E34">
-        <v>-37.34341956743776</v>
+        <v>-40.46013263137981</v>
       </c>
       <c r="F34">
-        <v>1.175939448990434</v>
+        <v>-0.07081064957361509</v>
       </c>
       <c r="G34">
-        <v>-7.585733251739336</v>
+        <v>-9.19691903109292</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.475734548614314</v>
       </c>
       <c r="E35">
-        <v>-37.63258067611196</v>
+        <v>-39.20105131596177</v>
       </c>
       <c r="F35">
-        <v>1.150135804393229</v>
+        <v>-0.6032322005793581</v>
       </c>
       <c r="G35">
-        <v>-6.367818289240397</v>
+        <v>-8.395934758305591</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>2.218439001346158</v>
       </c>
       <c r="E36">
-        <v>-37.36393850798807</v>
+        <v>-39.44696503511053</v>
       </c>
       <c r="F36">
-        <v>0.803584987962445</v>
+        <v>-0.9160908296360782</v>
       </c>
       <c r="G36">
-        <v>-6.336544179783451</v>
+        <v>-8.410310823396555</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.981251080715116</v>
       </c>
       <c r="E37">
-        <v>-36.55876788807754</v>
+        <v>-38.26875920382088</v>
       </c>
       <c r="F37">
-        <v>0.8188004404170663</v>
+        <v>-0.888248572860584</v>
       </c>
       <c r="G37">
-        <v>-8.343172915491486</v>
+        <v>-8.613693048533463</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.77542694933805</v>
       </c>
       <c r="E38">
-        <v>-35.39198338793118</v>
+        <v>-38.16190122964437</v>
       </c>
       <c r="F38">
-        <v>1.539925742515342</v>
+        <v>-0.8376378096517426</v>
       </c>
       <c r="G38">
-        <v>-5.94102159571897</v>
+        <v>-8.169075412433097</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.613467049333454</v>
       </c>
       <c r="E39">
-        <v>-36.6430095499847</v>
+        <v>-38.06242974180907</v>
       </c>
       <c r="F39">
-        <v>0.9410227372305222</v>
+        <v>-1.213946896660697</v>
       </c>
       <c r="G39">
-        <v>-6.677510034127438</v>
+        <v>-7.936018158901301</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.507409359580423</v>
       </c>
       <c r="E40">
-        <v>-33.30722497168627</v>
+        <v>-36.82882630126319</v>
       </c>
       <c r="F40">
-        <v>1.041419209715017</v>
+        <v>-1.21231749797939</v>
       </c>
       <c r="G40">
-        <v>-5.631217588814512</v>
+        <v>-7.873066579948082</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.467542286465121</v>
       </c>
       <c r="E41">
-        <v>-34.49858609984731</v>
+        <v>-38.02555130185025</v>
       </c>
       <c r="F41">
-        <v>0.9724211752662347</v>
+        <v>-0.9428918285862534</v>
       </c>
       <c r="G41">
-        <v>-4.325030740945443</v>
+        <v>-8.23239641174596</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.503543305986677</v>
       </c>
       <c r="E42">
-        <v>-32.7377740137277</v>
+        <v>-36.68650197897831</v>
       </c>
       <c r="F42">
-        <v>0.6772208541349917</v>
+        <v>-1.038988245882816</v>
       </c>
       <c r="G42">
-        <v>-6.06537919282747</v>
+        <v>-7.608775683500502</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.626626272264958</v>
       </c>
       <c r="E43">
-        <v>-32.01124445025279</v>
+        <v>-36.56453669860773</v>
       </c>
       <c r="F43">
-        <v>0.7313132455377994</v>
+        <v>-1.353533430971636</v>
       </c>
       <c r="G43">
-        <v>-5.198635485279179</v>
+        <v>-8.149296411410823</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.843165450896679</v>
       </c>
       <c r="E44">
-        <v>-32.13634125196229</v>
+        <v>-35.29763488626504</v>
       </c>
       <c r="F44">
-        <v>1.173583572096872</v>
+        <v>-1.260923612073456</v>
       </c>
       <c r="G44">
-        <v>-5.55354271573971</v>
+        <v>-7.089490752094296</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>2.153818977545256</v>
       </c>
       <c r="E45">
-        <v>-33.40326798357292</v>
+        <v>-35.68965650321561</v>
       </c>
       <c r="F45">
-        <v>1.607339938489972</v>
+        <v>-0.6630676631857748</v>
       </c>
       <c r="G45">
-        <v>-6.915562947434329</v>
+        <v>-7.616735843758806</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>2.560102001618774</v>
       </c>
       <c r="E46">
-        <v>-31.6784850056962</v>
+        <v>-33.60921119693153</v>
       </c>
       <c r="F46">
-        <v>2.167090986848876</v>
+        <v>-0.890148847682606</v>
       </c>
       <c r="G46">
-        <v>-5.568630208731753</v>
+        <v>-7.957592046829966</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>3.061416006288258</v>
       </c>
       <c r="E47">
-        <v>-31.12628025776399</v>
+        <v>-33.74131861935734</v>
       </c>
       <c r="F47">
-        <v>1.013904158063628</v>
+        <v>-1.206748383930369</v>
       </c>
       <c r="G47">
-        <v>-6.292365159812632</v>
+        <v>-7.741367569049372</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>3.650258161727231</v>
       </c>
       <c r="E48">
-        <v>-29.07775238051122</v>
+        <v>-33.37314058862262</v>
       </c>
       <c r="F48">
-        <v>1.074005526606344</v>
+        <v>-0.6486341895593962</v>
       </c>
       <c r="G48">
-        <v>-6.40283881718559</v>
+        <v>-7.92522795150623</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>4.312026845398101</v>
       </c>
       <c r="E49">
-        <v>-30.08820377657405</v>
+        <v>-32.91976358077036</v>
       </c>
       <c r="F49">
-        <v>1.38860289884154</v>
+        <v>-1.011853414869312</v>
       </c>
       <c r="G49">
-        <v>-6.499953294485823</v>
+        <v>-8.216974743446253</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>5.038315772295451</v>
       </c>
       <c r="E50">
-        <v>-28.56137946328396</v>
+        <v>-32.52479526038483</v>
       </c>
       <c r="F50">
-        <v>1.176794324150123</v>
+        <v>-0.9881364277597596</v>
       </c>
       <c r="G50">
-        <v>-6.828588602125981</v>
+        <v>-8.734088840724947</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>5.812922135813767</v>
       </c>
       <c r="E51">
-        <v>-27.39154442941951</v>
+        <v>-31.03780855012249</v>
       </c>
       <c r="F51">
-        <v>1.119814243981156</v>
+        <v>-0.7727004322114838</v>
       </c>
       <c r="G51">
-        <v>-7.22178501275978</v>
+        <v>-8.351708744932132</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>6.609357498943506</v>
       </c>
       <c r="E52">
-        <v>-28.44709347065299</v>
+        <v>-31.2542656179499</v>
       </c>
       <c r="F52">
-        <v>0.8282189777868968</v>
+        <v>-0.6384154492784615</v>
       </c>
       <c r="G52">
-        <v>-7.813882305439839</v>
+        <v>-8.326456317874589</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>7.407206386685063</v>
       </c>
       <c r="E53">
-        <v>-26.8165157086517</v>
+        <v>-31.08770107776765</v>
       </c>
       <c r="F53">
-        <v>0.6785155923855672</v>
+        <v>-0.8416454511464866</v>
       </c>
       <c r="G53">
-        <v>-7.035651977136358</v>
+        <v>-7.945872414360458</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>8.185322243271674</v>
       </c>
       <c r="E54">
-        <v>-25.94885171793647</v>
+        <v>-28.96485563706841</v>
       </c>
       <c r="F54">
-        <v>0.6456443171076773</v>
+        <v>-0.8152072771187376</v>
       </c>
       <c r="G54">
-        <v>-7.227808000531478</v>
+        <v>-8.853858054214566</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>8.918689634998373</v>
       </c>
       <c r="E55">
-        <v>-26.51547849219415</v>
+        <v>-28.3382066527443</v>
       </c>
       <c r="F55">
-        <v>0.9247917063400687</v>
+        <v>-1.391252312290708</v>
       </c>
       <c r="G55">
-        <v>-7.846168078425842</v>
+        <v>-8.780101908771025</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>9.581275373653213</v>
       </c>
       <c r="E56">
-        <v>-23.13361818745807</v>
+        <v>-27.87662705252551</v>
       </c>
       <c r="F56">
-        <v>0.9864984509094095</v>
+        <v>-1.053503727882071</v>
       </c>
       <c r="G56">
-        <v>-7.298880300535355</v>
+        <v>-8.975035764411089</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>10.15843555500519</v>
       </c>
       <c r="E57">
-        <v>-23.77208721121263</v>
+        <v>-26.13712924692492</v>
       </c>
       <c r="F57">
-        <v>0.7230130041617483</v>
+        <v>-1.312067015522298</v>
       </c>
       <c r="G57">
-        <v>-7.31791001785998</v>
+        <v>-9.324805049516309</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>10.63311171349158</v>
       </c>
       <c r="E58">
-        <v>-23.60591722610624</v>
+        <v>-26.8121008450134</v>
       </c>
       <c r="F58">
-        <v>0.5122597695414981</v>
+        <v>-1.494737766820242</v>
       </c>
       <c r="G58">
-        <v>-9.640723420253154</v>
+        <v>-10.02192868097997</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>10.98820682003457</v>
       </c>
       <c r="E59">
-        <v>-22.56505601672301</v>
+        <v>-26.40453791128533</v>
       </c>
       <c r="F59">
-        <v>0.7897645062141381</v>
+        <v>-1.242998569844278</v>
       </c>
       <c r="G59">
-        <v>-7.958815180670903</v>
+        <v>-9.980689359418744</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>11.21836028003836</v>
       </c>
       <c r="E60">
-        <v>-21.41682598817031</v>
+        <v>-26.50936081191268</v>
       </c>
       <c r="F60">
-        <v>0.2907758635853831</v>
+        <v>-1.323813265293995</v>
       </c>
       <c r="G60">
-        <v>-8.140033489601553</v>
+        <v>-10.31486336170895</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>11.32138367585509</v>
       </c>
       <c r="E61">
-        <v>-21.10873661888321</v>
+        <v>-24.53698829411763</v>
       </c>
       <c r="F61">
-        <v>0.587187257859519</v>
+        <v>-2.134586144458039</v>
       </c>
       <c r="G61">
-        <v>-10.05659936914995</v>
+        <v>-10.48586582705457</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>11.29697118172418</v>
       </c>
       <c r="E62">
-        <v>-20.81494260297616</v>
+        <v>-24.27514493293249</v>
       </c>
       <c r="F62">
-        <v>0.3502518147389848</v>
+        <v>-1.920062181420245</v>
       </c>
       <c r="G62">
-        <v>-8.170399059940792</v>
+        <v>-11.00326057937681</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>11.1526766939274</v>
       </c>
       <c r="E63">
-        <v>-21.41921823789341</v>
+        <v>-23.82207941592959</v>
       </c>
       <c r="F63">
-        <v>-0.3403572606075602</v>
+        <v>-2.288258238086181</v>
       </c>
       <c r="G63">
-        <v>-9.107003682002683</v>
+        <v>-11.28473800746769</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>10.90387398599461</v>
       </c>
       <c r="E64">
-        <v>-20.38765606866648</v>
+        <v>-22.95626775746524</v>
       </c>
       <c r="F64">
-        <v>0.5153073332163975</v>
+        <v>-2.328308145276731</v>
       </c>
       <c r="G64">
-        <v>-9.401908169525658</v>
+        <v>-11.22840336068065</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>10.56429714826472</v>
       </c>
       <c r="E65">
-        <v>-17.97622266245585</v>
+        <v>-22.67155266151427</v>
       </c>
       <c r="F65">
-        <v>0.1633331953994848</v>
+        <v>-2.555545891212692</v>
       </c>
       <c r="G65">
-        <v>-11.12093467033206</v>
+        <v>-10.96976211552824</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>10.15441038460215</v>
       </c>
       <c r="E66">
-        <v>-21.09246433691253</v>
+        <v>-22.31314298381553</v>
       </c>
       <c r="F66">
-        <v>-1.075708116114112</v>
+        <v>-2.255104489523936</v>
       </c>
       <c r="G66">
-        <v>-9.717181686348498</v>
+        <v>-11.50445827225579</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>9.699671686139135</v>
       </c>
       <c r="E67">
-        <v>-18.92204593709303</v>
+        <v>-21.4969497410489</v>
       </c>
       <c r="F67">
-        <v>-0.3588795557341571</v>
+        <v>-2.753941540917979</v>
       </c>
       <c r="G67">
-        <v>-9.143868701001498</v>
+        <v>-11.09826818579202</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>9.221904396491869</v>
       </c>
       <c r="E68">
-        <v>-19.42966388484755</v>
+        <v>-21.75804137098425</v>
       </c>
       <c r="F68">
-        <v>-1.588484934162465</v>
+        <v>-2.814940859725329</v>
       </c>
       <c r="G68">
-        <v>-10.79751040889577</v>
+        <v>-12.31860069778233</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>8.741797663478305</v>
       </c>
       <c r="E69">
-        <v>-17.98405561901448</v>
+        <v>-21.07516205853329</v>
       </c>
       <c r="F69">
-        <v>-1.077108057024843</v>
+        <v>-3.511989663261237</v>
       </c>
       <c r="G69">
-        <v>-9.377625634083714</v>
+        <v>-11.82106718493698</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>8.284020049729802</v>
       </c>
       <c r="E70">
-        <v>-19.41032237970783</v>
+        <v>-21.7604751528206</v>
       </c>
       <c r="F70">
-        <v>-0.5808546835601323</v>
+        <v>-3.034788740060915</v>
       </c>
       <c r="G70">
-        <v>-10.18544483621058</v>
+        <v>-11.63055723600656</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>7.870318424505927</v>
       </c>
       <c r="E71">
-        <v>-16.00862633768436</v>
+        <v>-20.66794799455651</v>
       </c>
       <c r="F71">
-        <v>-0.7181681777177895</v>
+        <v>-3.231230271062998</v>
       </c>
       <c r="G71">
-        <v>-9.459270144309304</v>
+        <v>-11.6935035934706</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>7.513250887648441</v>
       </c>
       <c r="E72">
-        <v>-18.49051482080937</v>
+        <v>-21.66213541507131</v>
       </c>
       <c r="F72">
-        <v>-1.153792512604202</v>
+        <v>-3.082377618984344</v>
       </c>
       <c r="G72">
-        <v>-10.43021780609499</v>
+        <v>-11.13004486358275</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>7.227435149610359</v>
       </c>
       <c r="E73">
-        <v>-18.80122071323112</v>
+        <v>-20.50925378983481</v>
       </c>
       <c r="F73">
-        <v>-1.230402415117309</v>
+        <v>-3.60919277940794</v>
       </c>
       <c r="G73">
-        <v>-8.400660206015505</v>
+        <v>-11.35435873347891</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>7.025444647053418</v>
       </c>
       <c r="E74">
-        <v>-19.65312742017995</v>
+        <v>-21.84547892900587</v>
       </c>
       <c r="F74">
-        <v>-1.452510081727732</v>
+        <v>-3.54249760633894</v>
       </c>
       <c r="G74">
-        <v>-10.18694079286128</v>
+        <v>-10.9938044624678</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>6.910782295776809</v>
       </c>
       <c r="E75">
-        <v>-20.02360217677731</v>
+        <v>-20.85305247009279</v>
       </c>
       <c r="F75">
-        <v>-1.069788602653707</v>
+        <v>-3.549079813721585</v>
       </c>
       <c r="G75">
-        <v>-8.706875744479479</v>
+        <v>-11.11309982581413</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>6.882088415569036</v>
       </c>
       <c r="E76">
-        <v>-18.12480795081292</v>
+        <v>-21.39542449021347</v>
       </c>
       <c r="F76">
-        <v>-1.456737240584218</v>
+        <v>-4.095528109958932</v>
       </c>
       <c r="G76">
-        <v>-8.960982126277125</v>
+        <v>-9.966219307522499</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>6.937492686283552</v>
       </c>
       <c r="E77">
-        <v>-19.46262792313271</v>
+        <v>-22.89847166866892</v>
       </c>
       <c r="F77">
-        <v>-1.367473197625946</v>
+        <v>-4.320986522713679</v>
       </c>
       <c r="G77">
-        <v>-8.756038675874732</v>
+        <v>-9.927611616509116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>7.07241381921149</v>
       </c>
       <c r="E78">
-        <v>-18.33693737243986</v>
+        <v>-22.35976278093674</v>
       </c>
       <c r="F78">
-        <v>-1.454730106367234</v>
+        <v>-4.147355744882486</v>
       </c>
       <c r="G78">
-        <v>-7.873233667601913</v>
+        <v>-9.987464241632683</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>7.273094400909497</v>
       </c>
       <c r="E79">
-        <v>-21.73038513677222</v>
+        <v>-22.38370189101305</v>
       </c>
       <c r="F79">
-        <v>-2.148036345977295</v>
+        <v>-3.602709147746228</v>
       </c>
       <c r="G79">
-        <v>-7.375941648631246</v>
+        <v>-10.08133486877846</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>7.525455943471676</v>
       </c>
       <c r="E80">
-        <v>-20.92758184731684</v>
+        <v>-22.95684505383939</v>
       </c>
       <c r="F80">
-        <v>-0.8942989683706316</v>
+        <v>-4.258956714857247</v>
       </c>
       <c r="G80">
-        <v>-7.726593365408262</v>
+        <v>-9.41791856073066</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>7.820414247816976</v>
       </c>
       <c r="E81">
-        <v>-23.63478619802513</v>
+        <v>-23.94699139973514</v>
       </c>
       <c r="F81">
-        <v>-1.015783189828193</v>
+        <v>-4.075648120659147</v>
       </c>
       <c r="G81">
-        <v>-6.348443953629745</v>
+        <v>-8.927816532363918</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>8.144208041869154</v>
       </c>
       <c r="E82">
-        <v>-23.91620364418418</v>
+        <v>-24.20748081402838</v>
       </c>
       <c r="F82">
-        <v>-1.68787245515035</v>
+        <v>-4.078181268176908</v>
       </c>
       <c r="G82">
-        <v>-6.529499091023451</v>
+        <v>-8.591886804336189</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>8.482776601716392</v>
       </c>
       <c r="E83">
-        <v>-22.59910819637528</v>
+        <v>-26.30287560447618</v>
       </c>
       <c r="F83">
-        <v>-1.426025519125426</v>
+        <v>-4.264657539323313</v>
       </c>
       <c r="G83">
-        <v>-5.935116091453872</v>
+        <v>-8.200067561474203</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>8.825991356365922</v>
       </c>
       <c r="E84">
-        <v>-26.09402721979585</v>
+        <v>-26.22503611782624</v>
       </c>
       <c r="F84">
-        <v>-1.808751968403868</v>
+        <v>-4.242410075986327</v>
       </c>
       <c r="G84">
-        <v>-5.78556480904113</v>
+        <v>-7.933380001491981</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>9.168091847674534</v>
       </c>
       <c r="E85">
-        <v>-27.52231659440438</v>
+        <v>-27.54849428538478</v>
       </c>
       <c r="F85">
-        <v>-1.381969627174937</v>
+        <v>-4.0577918329244</v>
       </c>
       <c r="G85">
-        <v>-6.216277619449227</v>
+        <v>-8.381567830820694</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>9.498078810490748</v>
       </c>
       <c r="E86">
-        <v>-26.74330705262894</v>
+        <v>-28.12872490333694</v>
       </c>
       <c r="F86">
-        <v>-1.113769941537944</v>
+        <v>-4.233351050069311</v>
       </c>
       <c r="G86">
-        <v>-5.095367482977693</v>
+        <v>-7.624301781583853</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>9.80435950296615</v>
       </c>
       <c r="E87">
-        <v>-29.34601452979888</v>
+        <v>-31.0343219292153</v>
       </c>
       <c r="F87">
-        <v>-1.858427504814948</v>
+        <v>-4.068593743856907</v>
       </c>
       <c r="G87">
-        <v>-5.995648815543425</v>
+        <v>-7.524438190229178</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>10.08249694536947</v>
       </c>
       <c r="E88">
-        <v>-29.40262487676196</v>
+        <v>-31.45053392552733</v>
       </c>
       <c r="F88">
-        <v>-1.880788454486118</v>
+        <v>-4.047234290375721</v>
       </c>
       <c r="G88">
-        <v>-5.994844706209362</v>
+        <v>-7.729897262688316</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>10.32093726267209</v>
       </c>
       <c r="E89">
-        <v>-31.52181964470669</v>
+        <v>-33.15113483046523</v>
       </c>
       <c r="F89">
-        <v>-2.321459203590385</v>
+        <v>-3.788310662915277</v>
       </c>
       <c r="G89">
-        <v>-5.566014242651458</v>
+        <v>-7.666136352911852</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>10.50660426861112</v>
       </c>
       <c r="E90">
-        <v>-35.85654084066987</v>
+        <v>-34.56287781115565</v>
       </c>
       <c r="F90">
-        <v>-1.369602930218543</v>
+        <v>-4.051090340635753</v>
       </c>
       <c r="G90">
-        <v>-5.786674375492353</v>
+        <v>-7.29598237403922</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>10.62918824982894</v>
       </c>
       <c r="E91">
-        <v>-35.12600965808349</v>
+        <v>-36.00967597203329</v>
       </c>
       <c r="F91">
-        <v>-1.546938995442459</v>
+        <v>-4.004715019957425</v>
       </c>
       <c r="G91">
-        <v>-6.323639269269578</v>
+        <v>-8.080601194357154</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>10.67878390982517</v>
       </c>
       <c r="E92">
-        <v>-35.99580839941968</v>
+        <v>-37.39163835091902</v>
       </c>
       <c r="F92">
-        <v>-1.619510606866918</v>
+        <v>-3.99419723904408</v>
       </c>
       <c r="G92">
-        <v>-6.878957697522329</v>
+        <v>-8.076499714604516</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>10.63939845224651</v>
       </c>
       <c r="E93">
-        <v>-37.49904870220173</v>
+        <v>-38.91110940355851</v>
       </c>
       <c r="F93">
-        <v>-1.38416894262937</v>
+        <v>-3.321666453896231</v>
       </c>
       <c r="G93">
-        <v>-7.25693868867912</v>
+        <v>-8.259592538151587</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>10.50070532831206</v>
       </c>
       <c r="E94">
-        <v>-41.40813841856818</v>
+        <v>-39.86244191301807</v>
       </c>
       <c r="F94">
-        <v>-1.366922333303084</v>
+        <v>-3.144849775033871</v>
       </c>
       <c r="G94">
-        <v>-7.127202957712927</v>
+        <v>-8.456176384373235</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>10.25871787562773</v>
       </c>
       <c r="E95">
-        <v>-42.16944489707154</v>
+        <v>-43.30125935786285</v>
       </c>
       <c r="F95">
-        <v>-1.805699434524551</v>
+        <v>-3.189298313133287</v>
       </c>
       <c r="G95">
-        <v>-8.599784306724308</v>
+        <v>-8.546696120836314</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>9.897040248171249</v>
       </c>
       <c r="E96">
-        <v>-45.55766376834594</v>
+        <v>-45.54055461429331</v>
       </c>
       <c r="F96">
-        <v>-0.2389046196844964</v>
+        <v>-3.254962997153204</v>
       </c>
       <c r="G96">
-        <v>-6.205980842781876</v>
+        <v>-8.552583349889275</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>9.422769738545034</v>
       </c>
       <c r="E97">
-        <v>-47.1692790057409</v>
+        <v>-46.80926722677362</v>
       </c>
       <c r="F97">
-        <v>-0.8933190097331198</v>
+        <v>-2.774926572333099</v>
       </c>
       <c r="G97">
-        <v>-8.315651751384266</v>
+        <v>-9.709935564735863</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>8.818112059776096</v>
       </c>
       <c r="E98">
-        <v>-48.98771066917551</v>
+        <v>-48.56789057052504</v>
       </c>
       <c r="F98">
-        <v>-0.2489112979103144</v>
+        <v>-2.946073904690699</v>
       </c>
       <c r="G98">
-        <v>-8.455925752892487</v>
+        <v>-9.523557119120877</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>8.119568543892361</v>
       </c>
       <c r="E99">
-        <v>-50.46557900397419</v>
+        <v>-52.09944714764758</v>
       </c>
       <c r="F99">
-        <v>0.2917665909991313</v>
+        <v>-2.279955511607922</v>
       </c>
       <c r="G99">
-        <v>-9.355776312600685</v>
+        <v>-10.16090905854329</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>7.281831293429153</v>
       </c>
       <c r="E100">
-        <v>-53.12225019419046</v>
+        <v>-53.03059193515999</v>
       </c>
       <c r="F100">
-        <v>0.5609528622128587</v>
+        <v>-2.02072207473883</v>
       </c>
       <c r="G100">
-        <v>-7.683882889269944</v>
+        <v>-11.20929140490141</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>6.401810101912103</v>
       </c>
       <c r="E101">
-        <v>-56.06785406645806</v>
+        <v>-56.39393410890149</v>
       </c>
       <c r="F101">
-        <v>1.152163647795283</v>
+        <v>-1.861778250959272</v>
       </c>
       <c r="G101">
-        <v>-9.219994097161475</v>
+        <v>-11.25209064635582</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>5.365887457716785</v>
       </c>
       <c r="E102">
-        <v>-56.96546219167389</v>
+        <v>-57.75081732120225</v>
       </c>
       <c r="F102">
-        <v>0.7631043297224388</v>
+        <v>-1.08013408314727</v>
       </c>
       <c r="G102">
-        <v>-10.41499063826733</v>
+        <v>-11.22285291767994</v>
       </c>
     </row>
   </sheetData>
